--- a/config_table/excels/Modules.xlsx
+++ b/config_table/excels/Modules.xlsx
@@ -1,95 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25522"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10814"/>
   <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shopiii/Documents/GitHub/Core/config_table/excels/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA556FFF-F516-694F-9E4C-DE28E6386A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-45740" yWindow="-6040" windowWidth="33600" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Modules" sheetId="4" r:id="rId5"/>
+    <sheet name="Modules" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="21">
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模块名称</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">场景路径</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模块描述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">模块类型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">船体</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>模块名称</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>场景路径</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>模块描述</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>模块类型</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>船体</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">res://scenes/Body/ShipBody.tscn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">普通的船体，可以当做填充物或者临时护盾</t>
+    <t>res://scenes/Body/ShipBody.tscn</t>
+  </si>
+  <si>
+    <t>普通的船体，可以当做填充物或者临时护盾</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">典型的跟踪导弹发射器，只需要用到很少的电力维持</t>
+    <t>典型的跟踪导弹发射器，只需要用到很少的电力维持</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">res://scenes/Weapon/MissileLauncher/AIM120MissileLauncher.tscn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIM120导弹发射器</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小型电力推进器</t>
+    <t>res://scenes/Weapon/MissileLauncher/AIM120MissileLauncher.tscn</t>
+  </si>
+  <si>
+    <t>AIM120导弹发射器</t>
+  </si>
+  <si>
+    <t>小型电力推进器</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">均衡的推进器，只要有电，哪里都能去到</t>
+    <t>均衡的推进器，只要有电，哪里都能去到</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">res://scenes/Engine/SmallEleEngine.tscn</t>
+    <t>res://scenes/Engine/SmallEleEngine.tscn</t>
+  </si>
+  <si>
+    <t>小型储存箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://scenes/Body/SmallStore.tscn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -140,6 +152,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -149,33 +166,18 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFF"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -197,38 +199,8 @@
         <fgColor rgb="FF525252"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="00A9D08E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D08E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="00525252"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00525252"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -251,77 +223,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin">
-        <color indexed="0"/>
-      </top>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin">
-        <color indexed="0"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="0"/>
-      </left>
-      <right style="thin"/>
-      <top style="thin">
-        <color indexed="0"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -337,29 +248,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -368,11 +273,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -673,70 +578,66 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.5625" style="10" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="21.5625" style="10" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="21.5625" style="10" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="21.5625" style="10" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="21.5625" style="10" customWidth="1" collapsed="1"/>
+    <col min="1" max="5" width="21.5" style="7" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:5" ht="20" customHeight="1">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:5" ht="14" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -753,7 +654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -770,69 +671,82 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="B7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>